--- a/output/mpbart_dgp2_output.xlsx
+++ b/output/mpbart_dgp2_output.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5cac48941448979/Bureaublad/msc_thesis/thesis_code/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_42CED8006D2F2BC7A4AC3C9E04D435EDE9E2BF75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{879F2E81-6516-40D6-9123-3314EA75F62C}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_42CED8001E9F2CC42CFE38A7A07438EDE9E2BF07" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C4ACFCB-EC4A-4399-BDDF-6923D9D91E6C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misclassification_rates" sheetId="1" r:id="rId1"/>
@@ -378,52 +378,52 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>0.23499999999999999</v>
+        <v>0.20799999999999999</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.252</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.29399999999999998</v>
+        <v>0.20499999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.26400000000000001</v>
+        <v>0.19900000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.28399999999999997</v>
+        <v>0.20799999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.26300000000000001</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.23899999999999999</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.29299999999999998</v>
+        <v>0.19800000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.25600000000000001</v>
+        <v>0.20599999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -432,7 +432,7 @@
       </c>
       <c r="B12">
         <f>AVERAGE(A1:A10)</f>
-        <v>0.26300000000000001</v>
+        <v>0.20119999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -441,7 +441,7 @@
       </c>
       <c r="B13">
         <f>_xlfn.STDEV.S(A1:A10)</f>
-        <v>2.1087120871912942E-2</v>
+        <v>1.3717790557439553E-2</v>
       </c>
     </row>
   </sheetData>
@@ -457,52 +457,52 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>0.33644609777777801</v>
+        <v>0.29126006399999999</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.35835095022222202</v>
+        <v>0.27313334577777798</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.34312948977777802</v>
+        <v>0.30978835644444402</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.38376114755555601</v>
+        <v>0.28370635199999999</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.35744940088888899</v>
+        <v>0.28141376977777799</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.37672024177777802</v>
+        <v>0.308641629333333</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.35269628533333303</v>
+        <v>0.28690227288888898</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.337103952888889</v>
+        <v>0.26983219288888899</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.37946531022222202</v>
+        <v>0.286778023111111</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.34515731466666699</v>
+        <v>0.29252121599999997</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -511,7 +511,7 @@
       </c>
       <c r="B12">
         <f>AVERAGE(A1:A10)</f>
-        <v>0.35702801911111115</v>
+        <v>0.28839772222222215</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -520,7 +520,7 @@
       </c>
       <c r="B13">
         <f>_xlfn.STDEV.S(A1:A10)</f>
-        <v>1.7579135648926787E-2</v>
+        <v>1.3105959699618534E-2</v>
       </c>
     </row>
   </sheetData>
